--- a/docs/qa-reports/TC_report_2026-04-17.xlsx
+++ b/docs/qa-reports/TC_report_2026-04-17.xlsx
@@ -1016,22 +1016,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>selectedVoiceURI 'ko-KR-SMTg01' 그대로 (setVoice 미노출)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>state.selectedVoiceURI = 'kor-x-lvariant-g01'로 변경 확인</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>PlayerContext에서 window.__debug__에 setVoice 노출 누락. VM 테스트는 React hook으로 직접 호출이라 통과했으나 CDP는 __debug__ 경유 필요. 또한 실기기 실제 voiceURI 포맷이 'ko-KR-SMTg01'이라 요청값과 다름.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>① __debug__에 setVoice 노출 추가 ② UI 바텀시트 직접 클릭 경로로 재테스트 ③ 실제 voiceURI 포맷 확인 후 비교 대조</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4517eec</t>
+          <t>4517eec + 신규</t>
         </is>
       </c>
     </row>
